--- a/artfynd/A 13129-2022 artfynd.xlsx
+++ b/artfynd/A 13129-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13129-2022 artfynd.xlsx
+++ b/artfynd/A 13129-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95478497</v>
+        <v>95478441</v>
       </c>
       <c r="B2" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1114</v>
+        <v>226</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Skuggorangelav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Caloplaca lucifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+          <t>G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614986.3063427089</v>
+        <v>615008</v>
       </c>
       <c r="R2" t="n">
-        <v>6465161.03721761</v>
+        <v>6465438</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95478494</v>
+        <v>95478460</v>
       </c>
       <c r="B3" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1114</v>
+        <v>655</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>615007.1292174304</v>
+        <v>614948</v>
       </c>
       <c r="R3" t="n">
-        <v>6465440.248838513</v>
+        <v>6465380</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,27 +840,18 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,15 +870,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95478460</v>
+        <v>95478494</v>
       </c>
       <c r="B4" t="n">
-        <v>88270</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +881,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>655</v>
+        <v>1114</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614947.776501496</v>
+        <v>615007</v>
       </c>
       <c r="R4" t="n">
-        <v>6465380.696229742</v>
+        <v>6465440</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,28 +938,17 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,12 +970,7 @@
         <v>95478496</v>
       </c>
       <c r="B5" t="n">
-        <v>73548</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614956.0669782648</v>
+        <v>614956</v>
       </c>
       <c r="R5" t="n">
-        <v>6465168.5665655</v>
+        <v>6465169</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1085,19 +1035,9 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,37 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95478504</v>
+        <v>95478497</v>
       </c>
       <c r="B6" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1114</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614965.5639083171</v>
+        <v>614987</v>
       </c>
       <c r="R6" t="n">
-        <v>6465149.918692148</v>
+        <v>6465161</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1197,19 +1132,9 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,12 +1164,7 @@
         <v>95478451</v>
       </c>
       <c r="B7" t="n">
-        <v>73615</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>614948.7982554835</v>
+        <v>614949</v>
       </c>
       <c r="R7" t="n">
-        <v>6465381.777330454</v>
+        <v>6465381</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1309,19 +1229,9 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,37 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95478431</v>
+        <v>95478504</v>
       </c>
       <c r="B8" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1388,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>614940.678537522</v>
+        <v>614965</v>
       </c>
       <c r="R8" t="n">
-        <v>6465154.450150677</v>
+        <v>6465150</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1421,19 +1326,9 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,15 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95478441</v>
+        <v>95478430</v>
       </c>
       <c r="B9" t="n">
-        <v>78840</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>226</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggorangelav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Caloplaca lucifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>G.Thor</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1500,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>615008.2428525377</v>
+        <v>614900</v>
       </c>
       <c r="R9" t="n">
-        <v>6465438.178718784</v>
+        <v>6465147</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1533,19 +1423,9 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,37 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95478482</v>
+        <v>95478431</v>
       </c>
       <c r="B10" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221141</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1612,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>614950.6460575925</v>
+        <v>614940</v>
       </c>
       <c r="R10" t="n">
-        <v>6465155.792064869</v>
+        <v>6465155</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1645,19 +1520,9 @@
           <t>2021-08-13</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-08-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,6 +1546,394 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>95478433</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Småskär, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>614941</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6465129</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sankt Anna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>95478434</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Småskär, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>615063</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6465246</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sankt Anna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>95478459</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Småskär, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>614943</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6465438</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sankt Anna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>95478482</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Småskär, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>614950</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6465155</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sankt Anna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-08-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13129-2022 artfynd.xlsx
+++ b/artfynd/A 13129-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478441</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478460</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478494</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478496</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478497</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478451</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478504</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478430</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478431</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478433</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478434</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478459</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,8 +1999,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95478482</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>